--- a/artfynd/A 17215-2025 artfynd.xlsx
+++ b/artfynd/A 17215-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101311243</v>
+        <v>101311213</v>
       </c>
       <c r="B2" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561673.0888771033</v>
+        <v>561614</v>
       </c>
       <c r="R2" t="n">
-        <v>7043603.099287762</v>
+        <v>7043334</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,19 +746,9 @@
           <t>2022-05-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-05-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,6 +773,107 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>101311243</v>
+      </c>
+      <c r="B3" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>561673</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7043603</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-05-31</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-05-31</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Maria Johansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
